--- a/8DIO/Claire Woodwinds/Claire Bassoon/xlsx/Claire Bassoon.xlsx
+++ b/8DIO/Claire Woodwinds/Claire Bassoon/xlsx/Claire Bassoon.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="30" windowWidth="21555" windowHeight="10530" tabRatio="730" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="30" windowWidth="21555" windowHeight="10530" tabRatio="730"/>
   </bookViews>
   <sheets>
     <sheet name="Bassoon Arcs" sheetId="1" r:id="rId1"/>
@@ -26,6 +26,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -54,6 +69,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
@@ -76,6 +106,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -104,6 +149,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
@@ -126,6 +186,21 @@
   </authors>
   <commentList>
     <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -154,6 +229,21 @@
       <text>
         <r>
           <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="ＭＳ Ｐゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>Since 0.7
+Enter valid filename. The converter will use as output filename and VST Expression Map name</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0">
+      <text>
+        <r>
+          <rPr>
             <b/>
             <sz val="9"/>
             <color indexed="81"/>
@@ -170,7 +260,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="395" uniqueCount="187">
   <si>
     <t>Name</t>
     <phoneticPr fontId="1"/>
@@ -739,13 +829,34 @@
   </si>
   <si>
     <t>STRONG 3</t>
+  </si>
+  <si>
+    <t>Expression Map Name</t>
+  </si>
+  <si>
+    <t>Bassoon Arcs</t>
+  </si>
+  <si>
+    <t>Bassoon Bonus FX Runs</t>
+  </si>
+  <si>
+    <t>Bassoon General Arts</t>
+  </si>
+  <si>
+    <t>Bassoon Leg Lyrical</t>
+  </si>
+  <si>
+    <t>Bassoon Leg Lyrical sus XFade</t>
+  </si>
+  <si>
+    <t>Bassoon Leg Strong</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -792,8 +903,15 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -839,6 +957,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -896,7 +1020,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -962,6 +1086,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1264,7 +1394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -1277,95 +1407,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>181</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>144</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>164</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>145</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>145</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -1373,25 +1464,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -1400,7 +1487,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -1411,13 +1498,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -1426,7 +1513,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -1437,13 +1524,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -1452,7 +1539,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -1462,14 +1549,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>167</v>
+      <c r="A8" s="17" t="s">
+        <v>165</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>167</v>
+      <c r="C8" s="17" t="s">
+        <v>165</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -1478,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -1488,14 +1575,14 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>168</v>
+      <c r="A9" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>168</v>
+      <c r="C9" s="17" t="s">
+        <v>166</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
@@ -1504,7 +1591,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="6">
         <v>120</v>
@@ -1515,13 +1602,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
@@ -1530,7 +1617,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="6">
         <v>120</v>
@@ -1540,25 +1627,53 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6">
+        <v>120</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6">
+        <v>120</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="3"/>
@@ -1566,7 +1681,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -2955,17 +3070,44 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -2980,19 +3122,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3002,7 +3144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -3015,95 +3157,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>182</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>170</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>147</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>171</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>148</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -3111,25 +3214,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -3138,7 +3237,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -3149,13 +3248,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -3164,7 +3263,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -3175,13 +3274,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -3190,7 +3289,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -3200,14 +3299,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>152</v>
+      <c r="A8" s="17" t="s">
+        <v>173</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>152</v>
+      <c r="C8" s="17" t="s">
+        <v>150</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -3216,7 +3315,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -3226,25 +3325,53 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="17" t="s">
+        <v>151</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="6">
+        <v>120</v>
+      </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="3"/>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="6"/>
+      <c r="A10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B10" s="6">
+        <v>1</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="6">
+        <v>1</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G10" s="6">
+        <v>120</v>
+      </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
       <c r="J10" s="3"/>
@@ -3264,7 +3391,7 @@
     <row r="12" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="6"/>
       <c r="F12" s="2"/>
@@ -3276,7 +3403,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -4665,18 +4792,45 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4690,19 +4844,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="Choose from Drop-down list" prompt="If don’t use MIDI Note, set Cell value empty">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4712,7 +4866,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J127"/>
+  <dimension ref="A1:J129"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -4725,95 +4879,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>183</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>154</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>154</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -4821,25 +4936,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -4848,7 +4959,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -4859,13 +4970,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -4874,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -4884,14 +4995,14 @@
       <c r="J6" s="3"/>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="3" t="s">
-        <v>157</v>
+      <c r="A7" s="17" t="s">
+        <v>174</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>157</v>
+      <c r="C7" s="17" t="s">
+        <v>155</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -4900,7 +5011,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -4910,25 +5021,53 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="6"/>
+      <c r="A8" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="B8" s="6">
+        <v>1</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>156</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="6">
+        <v>1</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="6">
+        <v>120</v>
+      </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="6"/>
+      <c r="A9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="6">
+        <v>1</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="6">
+        <v>120</v>
+      </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
       <c r="J9" s="3"/>
@@ -4948,7 +5087,7 @@
     <row r="11" spans="1:10">
       <c r="A11" s="3"/>
       <c r="B11" s="6"/>
-      <c r="C11" s="18"/>
+      <c r="C11" s="3"/>
       <c r="D11" s="2"/>
       <c r="E11" s="6"/>
       <c r="F11" s="2"/>
@@ -4960,7 +5099,7 @@
     <row r="12" spans="1:10">
       <c r="A12" s="3"/>
       <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
+      <c r="C12" s="3"/>
       <c r="D12" s="2"/>
       <c r="E12" s="6"/>
       <c r="F12" s="2"/>
@@ -6349,17 +6488,44 @@
       <c r="I127" s="6"/>
       <c r="J127" s="3"/>
     </row>
+    <row r="128" spans="1:10">
+      <c r="A128" s="3"/>
+      <c r="B128" s="6"/>
+      <c r="C128" s="18"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="6"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="6"/>
+      <c r="H128" s="6"/>
+      <c r="I128" s="6"/>
+      <c r="J128" s="3"/>
+    </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B127">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B129">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I127">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I129">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G127">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G129">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -6374,19 +6540,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F127</xm:sqref>
+          <xm:sqref>F4:F129</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D127</xm:sqref>
+          <xm:sqref>D4:D129</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E127</xm:sqref>
+          <xm:sqref>E4:E129</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6396,7 +6562,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -6409,95 +6575,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>184</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>175</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -6505,25 +6632,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -6532,7 +6655,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -6543,13 +6666,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -6558,7 +6681,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -6569,13 +6692,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -6584,7 +6707,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -6594,14 +6717,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>162</v>
+      <c r="A8" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>162</v>
+      <c r="C8" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -6610,7 +6733,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -6620,14 +6743,14 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>153</v>
+      <c r="A9" s="17" t="s">
+        <v>161</v>
       </c>
       <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>153</v>
+      <c r="C9" s="17" t="s">
+        <v>161</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
@@ -6636,7 +6759,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="6">
         <v>120</v>
@@ -6647,13 +6770,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
@@ -6662,7 +6785,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="6">
         <v>120</v>
@@ -6672,25 +6795,53 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6">
+        <v>120</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6">
+        <v>120</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="3"/>
@@ -6698,7 +6849,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -8087,18 +8238,45 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
   </dataValidations>
@@ -8112,19 +8290,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" showInputMessage="1" showErrorMessage="1" promptTitle="Choose from Drop-down list" prompt="If don’t use MIDI Note, set Cell value empty">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8134,7 +8312,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -8147,95 +8325,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>175</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -8243,25 +8382,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -8270,7 +8405,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -8281,13 +8416,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -8296,7 +8431,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -8307,13 +8442,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -8322,7 +8457,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -8332,14 +8467,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>163</v>
+      <c r="A8" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>163</v>
+      <c r="C8" s="17" t="s">
+        <v>177</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -8348,7 +8483,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -8358,14 +8493,14 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>153</v>
+      <c r="A9" s="17" t="s">
+        <v>178</v>
       </c>
       <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>153</v>
+      <c r="C9" s="17" t="s">
+        <v>178</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
@@ -8374,7 +8509,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="6">
         <v>120</v>
@@ -8385,13 +8520,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
@@ -8400,7 +8535,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="6">
         <v>120</v>
@@ -8410,25 +8545,53 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6">
+        <v>120</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6">
+        <v>120</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="3"/>
@@ -8436,7 +8599,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -9825,17 +9988,44 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -9850,19 +10040,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9872,7 +10062,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="35.625" style="5" customWidth="1"/>
@@ -9885,95 +10075,56 @@
     <col min="10" max="10" width="50.625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="30" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="22"/>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C3" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E3" s="12" t="s">
         <v>141</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I3" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="16" t="s">
+      <c r="J3" s="16" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="7" t="s">
+    <row r="4" spans="1:10">
+      <c r="A4" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B4" s="6">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C4" s="17" t="s">
         <v>143</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="6">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="6">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G3" s="6">
-        <v>120</v>
-      </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="B4" s="6">
-        <v>1</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>159</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>11</v>
@@ -9981,25 +10132,21 @@
       <c r="E4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G4" s="6">
-        <v>120</v>
-      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="6"/>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
       <c r="J4" s="3"/>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B5" s="6">
         <v>1</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>11</v>
@@ -10008,7 +10155,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G5" s="6">
         <v>120</v>
@@ -10019,13 +10166,13 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>11</v>
@@ -10034,7 +10181,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G6" s="6">
         <v>120</v>
@@ -10045,13 +10192,13 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B7" s="6">
         <v>1</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>11</v>
@@ -10060,7 +10207,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="G7" s="6">
         <v>120</v>
@@ -10070,14 +10217,14 @@
       <c r="J7" s="3"/>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="3" t="s">
-        <v>179</v>
+      <c r="A8" s="17" t="s">
+        <v>161</v>
       </c>
       <c r="B8" s="6">
         <v>1</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>179</v>
+      <c r="C8" s="17" t="s">
+        <v>161</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
@@ -10086,7 +10233,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G8" s="6">
         <v>120</v>
@@ -10096,14 +10243,14 @@
       <c r="J8" s="3"/>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="3" t="s">
-        <v>153</v>
+      <c r="A9" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="B9" s="6">
         <v>1</v>
       </c>
-      <c r="C9" s="3" t="s">
-        <v>153</v>
+      <c r="C9" s="17" t="s">
+        <v>162</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>11</v>
@@ -10112,7 +10259,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G9" s="6">
         <v>120</v>
@@ -10123,13 +10270,13 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="3" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="B10" s="6">
         <v>1</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>154</v>
+        <v>179</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>11</v>
@@ -10138,7 +10285,7 @@
         <v>1</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" s="6">
         <v>120</v>
@@ -10148,25 +10295,53 @@
       <c r="J10" s="3"/>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="6"/>
+      <c r="A11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="6">
+        <v>1</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="6">
+        <v>1</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="6">
+        <v>120</v>
+      </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="3"/>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="6"/>
+      <c r="A12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B12" s="6">
+        <v>1</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="6">
+        <v>1</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G12" s="6">
+        <v>120</v>
+      </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
       <c r="J12" s="3"/>
@@ -10174,7 +10349,7 @@
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="18"/>
+      <c r="C13" s="3"/>
       <c r="D13" s="2"/>
       <c r="E13" s="6"/>
       <c r="F13" s="2"/>
@@ -11563,17 +11738,44 @@
       <c r="I128" s="6"/>
       <c r="J128" s="3"/>
     </row>
+    <row r="129" spans="1:10">
+      <c r="A129" s="3"/>
+      <c r="B129" s="6"/>
+      <c r="C129" s="18"/>
+      <c r="D129" s="2"/>
+      <c r="E129" s="6"/>
+      <c r="F129" s="2"/>
+      <c r="G129" s="6"/>
+      <c r="H129" s="6"/>
+      <c r="I129" s="6"/>
+      <c r="J129" s="3"/>
+    </row>
+    <row r="130" spans="1:10">
+      <c r="A130" s="3"/>
+      <c r="B130" s="6"/>
+      <c r="C130" s="18"/>
+      <c r="D130" s="2"/>
+      <c r="E130" s="6"/>
+      <c r="F130" s="2"/>
+      <c r="G130" s="6"/>
+      <c r="H130" s="6"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="3"/>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B128">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B130">
       <formula1>"0,1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16"</formula1>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H2:I128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use CC set cell value empty" sqref="H4:I130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G2:G128">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="0-127" prompt="If don't use MIDI Note on, set cell value empty" sqref="G4:G130">
       <formula1>0</formula1>
       <formula2>127</formula2>
     </dataValidation>
@@ -11588,19 +11790,19 @@
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$A$2:$A$130</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F128</xm:sqref>
+          <xm:sqref>F4:F130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$B$2:$B$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D2:D128</xm:sqref>
+          <xm:sqref>D4:D130</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>'DO NOT MODIFY!'!$C$2:$C$6</xm:f>
           </x14:formula1>
-          <xm:sqref>E2:E128</xm:sqref>
+          <xm:sqref>E4:E130</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
